--- a/data/trans_orig/IP07KS_C08_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C08_2023-Clase-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de divertirse con sus amigos/as en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de divertirse con sus amigos/as, percibida por el/la menor en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>30404</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>25051</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>34844</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>76,24%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>62,82%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>87,37%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>20789</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>15650</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24257</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>68,19%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>51,33%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>79,56%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>30215</t>
+          <t>21598</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25316</t>
+          <t>16293</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34107</t>
+          <t>25705</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>51004</t>
+          <t>52002</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44639</t>
+          <t>44459</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56994</t>
+          <t>57759</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>80,32%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9475</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5035</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14828</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>23,76%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>12,63%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>37,18%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9188</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5703</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14347</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>30,14%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>18,71%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>47,06%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8909</t>
+          <t>9850</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5017</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13808</t>
+          <t>15173</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>18097</t>
+          <t>19326</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>13676</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24431</t>
+          <t>27202</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>37,83%</t>
         </is>
       </c>
     </row>
@@ -946,107 +946,107 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2987</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3014</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,8%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>9,41%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>2621</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>2598</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23969</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18640</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28311</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>72,21%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>56,15%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>85,29%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>20486</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15267</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24241</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>70,23%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>52,34%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>83,11%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23845</t>
+          <t>21340</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18843</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27823</t>
+          <t>25472</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>44331</t>
+          <t>45309</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38203</t>
+          <t>38021</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50277</t>
+          <t>51372</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>80,31%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9226</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4884</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>14555</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>27,79%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>14,71%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>43,85%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>8682</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4927</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>13901</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>29,77%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>16,89%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>47,66%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8593</t>
+          <t>9431</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13595</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>17275</t>
+          <t>18657</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11329</t>
+          <t>12594</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23403</t>
+          <t>25945</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>40,56%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16347</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11501</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20498</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>60,61%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>42,64%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>76,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>8514</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5310</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11415</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>58,52%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>36,49%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>78,46%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16825</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10861</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21284</t>
+          <t>12024</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>25265</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19346</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30795</t>
+          <t>30961</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>72,78%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9697</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5636</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>14508</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>35,95%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20,9%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>53,79%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>5319</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8379</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>36,56%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>15,9%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>57,59%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>9458</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>15365</t>
+          <t>15595</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10005</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21318</t>
+          <t>21026</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>49,43%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>928</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>751</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1679</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>43056</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>31872</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>52086</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>62,03%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>45,92%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>75,04%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>27730</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>9972</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>49209</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>41,29%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>14,85%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>73,28%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>43503</t>
+          <t>28744</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31469</t>
+          <t>21567</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52968</t>
+          <t>34304</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>71234</t>
+          <t>71800</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39663</t>
+          <t>58710</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93672</t>
+          <t>83195</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>73,6%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>23324</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>14582</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>34943</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>33,6%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>21,01%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>50,34%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>38298</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>16493</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>56998</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>57,03%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>24,56%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>84,87%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>23952</t>
+          <t>13824</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14692</t>
+          <t>8317</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>36843</t>
+          <t>20989</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>62250</t>
+          <t>37148</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>38610</t>
+          <t>25850</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>96280</t>
+          <t>51185</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>45,28%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2403</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>9,24%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>1127</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>4523</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1048</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>4552</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>6,74%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>2709</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>6394</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>7422</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -3105,107 +3105,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>630</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3364</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>3884</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>4,75%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>3816</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>22793</t>
+          <t>35921</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18218</t>
+          <t>27556</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27449</t>
+          <t>46109</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>38653</t>
+          <t>24342</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>30051</t>
+          <t>18913</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>50716</t>
+          <t>29753</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>61446</t>
+          <t>60263</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>51600</t>
+          <t>50509</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>73197</t>
+          <t>71211</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>72,58%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>19350</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>10285</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>27562</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>32,72%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>17,39%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>46,6%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>12208</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>7553</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>16757</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>34,19%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>21,15%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>46,93%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>18371</t>
+          <t>13384</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>7819</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>26756</t>
+          <t>18706</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>30580</t>
+          <t>32734</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20008</t>
+          <t>21997</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>40392</t>
+          <t>42567</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>43,38%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>3568</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>979</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>8234</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>6,03%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>13,92%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>709</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>2471</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>6,92%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>336</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>4818</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9226</t>
+          <t>9500</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -3900,107 +3900,107 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>1869</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>1502</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>1733</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4130,72 +4130,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>18734</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>12728</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>51,3%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>34,85%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>66,51%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>16605</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>11699</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>21578</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>55,02%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>38,77%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>71,5%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>18735</t>
+          <t>17913</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>12888</t>
+          <t>12740</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23731</t>
+          <t>23401</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>35339</t>
+          <t>36647</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>28132</t>
+          <t>28915</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>42319</t>
+          <t>44063</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,26%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>12718</t>
+          <t>14024</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>8802</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>17793</t>
+          <t>19465</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>14089</t>
+          <t>14285</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19442</t>
+          <t>19646</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>26806</t>
+          <t>28309</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>19740</t>
+          <t>20894</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>33410</t>
+          <t>36462</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>52,35%</t>
         </is>
       </c>
     </row>
@@ -4356,72 +4356,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>7881</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>6,37%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>21,58%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>855</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>4793</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>4684</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>15,88%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>2156</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>7562</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>5,98%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>3011</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>921</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8758</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -4469,107 +4469,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
+          <t>3,93%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>1088</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>5225</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>1437</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>4939</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>14,49%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>1088</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>3999</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>168432</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>150609</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>187360</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>63,53%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>56,81%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>70,67%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>116917</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>75533</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>139037</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>56,41%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>36,45%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>67,09%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>171776</t>
+          <t>122854</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>152947</t>
+          <t>111261</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>189236</t>
+          <t>133399</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>288693</t>
+          <t>291286</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>230687</t>
+          <t>268595</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>317080</t>
+          <t>311835</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,91%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>85097</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>69071</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>102757</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>32,1%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>26,05%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>38,76%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>86413</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>63490</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>129549</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>41,7%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>30,64%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>62,51%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>83960</t>
+          <t>66672</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>67880</t>
+          <t>55832</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>103481</t>
+          <t>79158</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>170372</t>
+          <t>151769</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>142047</t>
+          <t>131667</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>230972</t>
+          <t>174664</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>38,04%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>9226</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>4869</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>16979</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>6,4%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>3916</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>1559</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>8189</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>9079</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>15483</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>12995</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>20049</t>
+          <t>20998</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -5151,107 +5151,107 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>456</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>5607</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>486</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -5264,107 +5264,107 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>1881</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>1933</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>265125</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>265125</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>265125</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>266883</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>266883</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>266883</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>474129</t>
+          <t>459214</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>474129</t>
+          <t>459214</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>474129</t>
+          <t>459214</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
